--- a/templates/1.2. Dozer _ Template_2026_05_01_BiT.xlsx
+++ b/templates/1.2. Dozer _ Template_2026_05_01_BiT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CONSULTANCY\CMI\analytics-2026\Analysis-Templates\NPN_Water_Template_2026__01_BiT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\CMI_DATA_PROCESSOR\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5FCCF5E-B6F3-45D3-99AD-47F5360F8091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49B797A-9A66-4623-B2E1-7EC28E831D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dozer" sheetId="22" r:id="rId1"/>
@@ -960,28 +960,10 @@
     <xf numFmtId="9" fontId="3" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="7" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="7" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -999,16 +981,34 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="7" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="7" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1442,72 +1442,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="108.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
     </row>
     <row r="2" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
     </row>
     <row r="3" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
     </row>
     <row r="5" spans="2:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:18" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1516,10 +1516,10 @@
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="11"/>
-      <c r="G6" s="46" t="s">
+      <c r="G6" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="47"/>
+      <c r="H6" s="56"/>
       <c r="I6" s="2"/>
       <c r="K6" s="3" t="s">
         <v>0</v>
@@ -1541,61 +1541,61 @@
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="2:18" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="40" t="s">
+      <c r="D9" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="40" t="s">
+      <c r="E9" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="40" t="s">
+      <c r="G9" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="48" t="s">
+      <c r="H9" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="49"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="40" t="s">
+      <c r="I9" s="43"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="L9" s="40" t="s">
+      <c r="L9" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="M9" s="40" t="s">
+      <c r="M9" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="N9" s="40" t="s">
+      <c r="N9" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="O9" s="40" t="s">
+      <c r="O9" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="P9" s="40" t="s">
+      <c r="P9" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="Q9" s="40" t="s">
+      <c r="Q9" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="R9" s="40" t="s">
+      <c r="R9" s="47" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="2:18" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
       <c r="H10" s="6" t="s">
         <v>17</v>
       </c>
@@ -1605,14 +1605,14 @@
       <c r="J10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="41"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
     </row>
     <row r="11" spans="2:18" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="7" t="s">
@@ -1627,7 +1627,10 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="L11" s="7">
+        <f>H11*I11*J11</f>
+        <v>0</v>
+      </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7" t="e">
         <f>L11*3600/M11*0.764555</f>
@@ -1663,7 +1666,10 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
+      <c r="L12" s="8">
+        <f>H12*I12*J12</f>
+        <v>0</v>
+      </c>
       <c r="M12" s="8"/>
       <c r="N12" s="8" t="e">
         <f t="shared" ref="N12:N21" si="0">L12*3600/M12*0.764555</f>
@@ -1687,7 +1693,10 @@
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
+      <c r="L13" s="8">
+        <f t="shared" ref="L13:L76" si="1">H13*I13*J13</f>
+        <v>0</v>
+      </c>
       <c r="M13" s="8"/>
       <c r="N13" s="8" t="e">
         <f t="shared" si="0"/>
@@ -1711,7 +1720,10 @@
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
+      <c r="L14" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M14" s="8"/>
       <c r="N14" s="8" t="e">
         <f t="shared" si="0"/>
@@ -1735,7 +1747,10 @@
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
+      <c r="L15" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M15" s="9"/>
       <c r="N15" s="9" t="e">
         <f t="shared" si="0"/>
@@ -1759,7 +1774,10 @@
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
+      <c r="L16" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7" t="e">
         <f t="shared" si="0"/>
@@ -1783,7 +1801,10 @@
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
+      <c r="L17" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M17" s="8"/>
       <c r="N17" s="8" t="e">
         <f t="shared" si="0"/>
@@ -1807,7 +1828,10 @@
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
+      <c r="L18" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M18" s="8"/>
       <c r="N18" s="8" t="e">
         <f t="shared" si="0"/>
@@ -1831,7 +1855,10 @@
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
+      <c r="L19" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M19" s="8"/>
       <c r="N19" s="8" t="e">
         <f t="shared" si="0"/>
@@ -1855,7 +1882,10 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
+      <c r="L20" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M20" s="9"/>
       <c r="N20" s="9" t="e">
         <f t="shared" si="0"/>
@@ -1879,7 +1909,10 @@
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
+      <c r="L21" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M21" s="7"/>
       <c r="N21" s="7" t="e">
         <f t="shared" si="0"/>
@@ -1899,10 +1932,13 @@
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
+      <c r="L22" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M22" s="8"/>
       <c r="N22" s="8" t="e">
-        <f t="shared" ref="N22:N85" si="1">L22*3600/M22*0.764555</f>
+        <f t="shared" ref="N22:N85" si="2">L22*3600/M22*0.764555</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1919,10 +1955,13 @@
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
+      <c r="L23" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M23" s="8"/>
       <c r="N23" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1939,10 +1978,13 @@
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
+      <c r="L24" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M24" s="8"/>
       <c r="N24" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1959,10 +2001,13 @@
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
+      <c r="L25" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M25" s="9"/>
       <c r="N25" s="9" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1979,10 +2024,13 @@
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
+      <c r="L26" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M26" s="7"/>
       <c r="N26" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1999,10 +2047,13 @@
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
+      <c r="L27" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M27" s="8"/>
       <c r="N27" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2019,10 +2070,13 @@
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
+      <c r="L28" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M28" s="8"/>
       <c r="N28" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2039,10 +2093,13 @@
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
+      <c r="L29" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M29" s="8"/>
       <c r="N29" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2059,10 +2116,13 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
+      <c r="L30" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M30" s="9"/>
       <c r="N30" s="9" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2079,10 +2139,13 @@
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
+      <c r="L31" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M31" s="7"/>
       <c r="N31" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2099,10 +2162,13 @@
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
+      <c r="L32" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M32" s="8"/>
       <c r="N32" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2119,10 +2185,13 @@
       <c r="I33" s="8"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
+      <c r="L33" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M33" s="8"/>
       <c r="N33" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2139,10 +2208,13 @@
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
+      <c r="L34" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M34" s="8"/>
       <c r="N34" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2159,10 +2231,13 @@
       <c r="I35" s="9"/>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
+      <c r="L35" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M35" s="9"/>
       <c r="N35" s="9" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2179,10 +2254,13 @@
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
+      <c r="L36" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M36" s="7"/>
       <c r="N36" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2199,10 +2277,13 @@
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
+      <c r="L37" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M37" s="8"/>
       <c r="N37" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2219,10 +2300,13 @@
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
+      <c r="L38" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M38" s="8"/>
       <c r="N38" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2239,10 +2323,13 @@
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
+      <c r="L39" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M39" s="8"/>
       <c r="N39" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2259,10 +2346,13 @@
       <c r="I40" s="9"/>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
+      <c r="L40" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M40" s="9"/>
       <c r="N40" s="9" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2279,10 +2369,13 @@
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
+      <c r="L41" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M41" s="7"/>
       <c r="N41" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2299,10 +2392,13 @@
       <c r="I42" s="8"/>
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
+      <c r="L42" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M42" s="8"/>
       <c r="N42" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2319,10 +2415,13 @@
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
+      <c r="L43" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M43" s="8"/>
       <c r="N43" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2339,10 +2438,13 @@
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
       <c r="K44" s="8"/>
-      <c r="L44" s="8"/>
+      <c r="L44" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M44" s="8"/>
       <c r="N44" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2359,10 +2461,13 @@
       <c r="I45" s="9"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
+      <c r="L45" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M45" s="9"/>
       <c r="N45" s="9" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2379,10 +2484,13 @@
       <c r="I46" s="7"/>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
+      <c r="L46" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M46" s="7"/>
       <c r="N46" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2399,10 +2507,13 @@
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
+      <c r="L47" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M47" s="8"/>
       <c r="N47" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2419,10 +2530,13 @@
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
+      <c r="L48" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M48" s="8"/>
       <c r="N48" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2439,10 +2553,13 @@
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
       <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
+      <c r="L49" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M49" s="8"/>
       <c r="N49" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2459,10 +2576,13 @@
       <c r="I50" s="9"/>
       <c r="J50" s="9"/>
       <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
+      <c r="L50" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M50" s="9"/>
       <c r="N50" s="9" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2479,10 +2599,13 @@
       <c r="I51" s="7"/>
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
+      <c r="L51" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M51" s="7"/>
       <c r="N51" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2499,10 +2622,13 @@
       <c r="I52" s="8"/>
       <c r="J52" s="8"/>
       <c r="K52" s="8"/>
-      <c r="L52" s="8"/>
+      <c r="L52" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M52" s="8"/>
       <c r="N52" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2519,10 +2645,13 @@
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
       <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
+      <c r="L53" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M53" s="8"/>
       <c r="N53" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2539,10 +2668,13 @@
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
       <c r="K54" s="8"/>
-      <c r="L54" s="8"/>
+      <c r="L54" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M54" s="8"/>
       <c r="N54" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2559,10 +2691,13 @@
       <c r="I55" s="9"/>
       <c r="J55" s="9"/>
       <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
+      <c r="L55" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M55" s="9"/>
       <c r="N55" s="9" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2579,10 +2714,13 @@
       <c r="I56" s="7"/>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
-      <c r="L56" s="7"/>
+      <c r="L56" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M56" s="7"/>
       <c r="N56" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2599,10 +2737,13 @@
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
       <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
+      <c r="L57" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M57" s="8"/>
       <c r="N57" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2619,10 +2760,13 @@
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
       <c r="K58" s="8"/>
-      <c r="L58" s="8"/>
+      <c r="L58" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M58" s="8"/>
       <c r="N58" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2639,10 +2783,13 @@
       <c r="I59" s="8"/>
       <c r="J59" s="8"/>
       <c r="K59" s="8"/>
-      <c r="L59" s="8"/>
+      <c r="L59" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M59" s="8"/>
       <c r="N59" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2659,10 +2806,13 @@
       <c r="I60" s="9"/>
       <c r="J60" s="9"/>
       <c r="K60" s="9"/>
-      <c r="L60" s="9"/>
+      <c r="L60" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M60" s="9"/>
       <c r="N60" s="9" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2679,10 +2829,13 @@
       <c r="I61" s="7"/>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
-      <c r="L61" s="7"/>
+      <c r="L61" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M61" s="7"/>
       <c r="N61" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2699,10 +2852,13 @@
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
       <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
+      <c r="L62" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M62" s="8"/>
       <c r="N62" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2719,10 +2875,13 @@
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
       <c r="K63" s="8"/>
-      <c r="L63" s="8"/>
+      <c r="L63" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M63" s="8"/>
       <c r="N63" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2739,10 +2898,13 @@
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
       <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
+      <c r="L64" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M64" s="8"/>
       <c r="N64" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2759,10 +2921,13 @@
       <c r="I65" s="9"/>
       <c r="J65" s="9"/>
       <c r="K65" s="9"/>
-      <c r="L65" s="9"/>
+      <c r="L65" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M65" s="9"/>
       <c r="N65" s="9" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2779,10 +2944,13 @@
       <c r="I66" s="7"/>
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
-      <c r="L66" s="7"/>
+      <c r="L66" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M66" s="7"/>
       <c r="N66" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2799,10 +2967,13 @@
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
       <c r="K67" s="8"/>
-      <c r="L67" s="8"/>
+      <c r="L67" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M67" s="8"/>
       <c r="N67" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2819,10 +2990,13 @@
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
       <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
+      <c r="L68" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M68" s="8"/>
       <c r="N68" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2839,10 +3013,13 @@
       <c r="I69" s="8"/>
       <c r="J69" s="8"/>
       <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
+      <c r="L69" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M69" s="8"/>
       <c r="N69" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2859,10 +3036,13 @@
       <c r="I70" s="9"/>
       <c r="J70" s="9"/>
       <c r="K70" s="9"/>
-      <c r="L70" s="9"/>
+      <c r="L70" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M70" s="9"/>
       <c r="N70" s="9" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2879,10 +3059,13 @@
       <c r="I71" s="7"/>
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
-      <c r="L71" s="7"/>
+      <c r="L71" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M71" s="7"/>
       <c r="N71" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2899,10 +3082,13 @@
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
       <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
+      <c r="L72" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M72" s="8"/>
       <c r="N72" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2919,10 +3105,13 @@
       <c r="I73" s="8"/>
       <c r="J73" s="8"/>
       <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
+      <c r="L73" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M73" s="8"/>
       <c r="N73" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2939,10 +3128,13 @@
       <c r="I74" s="8"/>
       <c r="J74" s="8"/>
       <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
+      <c r="L74" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M74" s="8"/>
       <c r="N74" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2959,10 +3151,13 @@
       <c r="I75" s="9"/>
       <c r="J75" s="9"/>
       <c r="K75" s="9"/>
-      <c r="L75" s="9"/>
+      <c r="L75" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M75" s="9"/>
       <c r="N75" s="9" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2979,10 +3174,13 @@
       <c r="I76" s="7"/>
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
+      <c r="L76" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M76" s="7"/>
       <c r="N76" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2999,10 +3197,13 @@
       <c r="I77" s="8"/>
       <c r="J77" s="8"/>
       <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
+      <c r="L77" s="8">
+        <f t="shared" ref="L77:L110" si="3">H77*I77*J77</f>
+        <v>0</v>
+      </c>
       <c r="M77" s="8"/>
       <c r="N77" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3019,10 +3220,13 @@
       <c r="I78" s="8"/>
       <c r="J78" s="8"/>
       <c r="K78" s="8"/>
-      <c r="L78" s="8"/>
+      <c r="L78" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M78" s="8"/>
       <c r="N78" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3039,10 +3243,13 @@
       <c r="I79" s="8"/>
       <c r="J79" s="8"/>
       <c r="K79" s="8"/>
-      <c r="L79" s="8"/>
+      <c r="L79" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M79" s="8"/>
       <c r="N79" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3059,10 +3266,13 @@
       <c r="I80" s="9"/>
       <c r="J80" s="9"/>
       <c r="K80" s="9"/>
-      <c r="L80" s="9"/>
+      <c r="L80" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M80" s="9"/>
       <c r="N80" s="9" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3079,10 +3289,13 @@
       <c r="I81" s="7"/>
       <c r="J81" s="7"/>
       <c r="K81" s="7"/>
-      <c r="L81" s="7"/>
+      <c r="L81" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M81" s="7"/>
       <c r="N81" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3099,10 +3312,13 @@
       <c r="I82" s="8"/>
       <c r="J82" s="8"/>
       <c r="K82" s="8"/>
-      <c r="L82" s="8"/>
+      <c r="L82" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M82" s="8"/>
       <c r="N82" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3119,10 +3335,13 @@
       <c r="I83" s="8"/>
       <c r="J83" s="8"/>
       <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
+      <c r="L83" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M83" s="8"/>
       <c r="N83" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3139,10 +3358,13 @@
       <c r="I84" s="8"/>
       <c r="J84" s="8"/>
       <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
+      <c r="L84" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M84" s="8"/>
       <c r="N84" s="8" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3159,10 +3381,13 @@
       <c r="I85" s="9"/>
       <c r="J85" s="9"/>
       <c r="K85" s="9"/>
-      <c r="L85" s="9"/>
+      <c r="L85" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M85" s="9"/>
       <c r="N85" s="9" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3179,10 +3404,13 @@
       <c r="I86" s="7"/>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
-      <c r="L86" s="7"/>
+      <c r="L86" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M86" s="7"/>
       <c r="N86" s="7" t="e">
-        <f t="shared" ref="N86:N109" si="2">L86*3600/M86*0.764555</f>
+        <f t="shared" ref="N86:N105" si="4">L86*3600/M86*0.764555</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3199,10 +3427,13 @@
       <c r="I87" s="8"/>
       <c r="J87" s="8"/>
       <c r="K87" s="8"/>
-      <c r="L87" s="8"/>
+      <c r="L87" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M87" s="8"/>
       <c r="N87" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3219,10 +3450,13 @@
       <c r="I88" s="8"/>
       <c r="J88" s="8"/>
       <c r="K88" s="8"/>
-      <c r="L88" s="8"/>
+      <c r="L88" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M88" s="8"/>
       <c r="N88" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3239,10 +3473,13 @@
       <c r="I89" s="8"/>
       <c r="J89" s="8"/>
       <c r="K89" s="8"/>
-      <c r="L89" s="8"/>
+      <c r="L89" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M89" s="8"/>
       <c r="N89" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3259,10 +3496,13 @@
       <c r="I90" s="9"/>
       <c r="J90" s="9"/>
       <c r="K90" s="9"/>
-      <c r="L90" s="9"/>
+      <c r="L90" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M90" s="9"/>
       <c r="N90" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3279,10 +3519,13 @@
       <c r="I91" s="7"/>
       <c r="J91" s="7"/>
       <c r="K91" s="7"/>
-      <c r="L91" s="7"/>
+      <c r="L91" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M91" s="7"/>
       <c r="N91" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3299,10 +3542,13 @@
       <c r="I92" s="8"/>
       <c r="J92" s="8"/>
       <c r="K92" s="8"/>
-      <c r="L92" s="8"/>
+      <c r="L92" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M92" s="8"/>
       <c r="N92" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3319,10 +3565,13 @@
       <c r="I93" s="8"/>
       <c r="J93" s="8"/>
       <c r="K93" s="8"/>
-      <c r="L93" s="8"/>
+      <c r="L93" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M93" s="8"/>
       <c r="N93" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3339,10 +3588,13 @@
       <c r="I94" s="8"/>
       <c r="J94" s="8"/>
       <c r="K94" s="8"/>
-      <c r="L94" s="8"/>
+      <c r="L94" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M94" s="8"/>
       <c r="N94" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3359,10 +3611,13 @@
       <c r="I95" s="9"/>
       <c r="J95" s="9"/>
       <c r="K95" s="9"/>
-      <c r="L95" s="9"/>
+      <c r="L95" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M95" s="9"/>
       <c r="N95" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3379,10 +3634,13 @@
       <c r="I96" s="7"/>
       <c r="J96" s="7"/>
       <c r="K96" s="7"/>
-      <c r="L96" s="7"/>
+      <c r="L96" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M96" s="7"/>
       <c r="N96" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3399,10 +3657,13 @@
       <c r="I97" s="8"/>
       <c r="J97" s="8"/>
       <c r="K97" s="8"/>
-      <c r="L97" s="8"/>
+      <c r="L97" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M97" s="8"/>
       <c r="N97" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3419,10 +3680,13 @@
       <c r="I98" s="8"/>
       <c r="J98" s="8"/>
       <c r="K98" s="8"/>
-      <c r="L98" s="8"/>
+      <c r="L98" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M98" s="8"/>
       <c r="N98" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3439,10 +3703,13 @@
       <c r="I99" s="8"/>
       <c r="J99" s="8"/>
       <c r="K99" s="8"/>
-      <c r="L99" s="8"/>
+      <c r="L99" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M99" s="8"/>
       <c r="N99" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3459,10 +3726,13 @@
       <c r="I100" s="9"/>
       <c r="J100" s="9"/>
       <c r="K100" s="9"/>
-      <c r="L100" s="9"/>
+      <c r="L100" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M100" s="9"/>
       <c r="N100" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3479,10 +3749,13 @@
       <c r="I101" s="7"/>
       <c r="J101" s="7"/>
       <c r="K101" s="7"/>
-      <c r="L101" s="7"/>
+      <c r="L101" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M101" s="7"/>
       <c r="N101" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3499,10 +3772,13 @@
       <c r="I102" s="8"/>
       <c r="J102" s="8"/>
       <c r="K102" s="8"/>
-      <c r="L102" s="8"/>
+      <c r="L102" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M102" s="8"/>
       <c r="N102" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3519,10 +3795,13 @@
       <c r="I103" s="8"/>
       <c r="J103" s="8"/>
       <c r="K103" s="8"/>
-      <c r="L103" s="8"/>
+      <c r="L103" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M103" s="8"/>
       <c r="N103" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3539,10 +3818,13 @@
       <c r="I104" s="8"/>
       <c r="J104" s="8"/>
       <c r="K104" s="8"/>
-      <c r="L104" s="8"/>
+      <c r="L104" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M104" s="8"/>
       <c r="N104" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3559,10 +3841,13 @@
       <c r="I105" s="9"/>
       <c r="J105" s="9"/>
       <c r="K105" s="9"/>
-      <c r="L105" s="9"/>
+      <c r="L105" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M105" s="9"/>
       <c r="N105" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3579,10 +3864,13 @@
       <c r="I106" s="7"/>
       <c r="J106" s="7"/>
       <c r="K106" s="7"/>
-      <c r="L106" s="7"/>
+      <c r="L106" s="7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M106" s="7"/>
       <c r="N106" s="7" t="e">
-        <f t="shared" ref="N106:N110" si="3">L106*3600/M106*0.764555</f>
+        <f t="shared" ref="N106:N110" si="5">L106*3600/M106*0.764555</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3599,10 +3887,13 @@
       <c r="I107" s="8"/>
       <c r="J107" s="8"/>
       <c r="K107" s="8"/>
-      <c r="L107" s="8"/>
+      <c r="L107" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M107" s="8"/>
       <c r="N107" s="8" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3619,10 +3910,13 @@
       <c r="I108" s="8"/>
       <c r="J108" s="8"/>
       <c r="K108" s="8"/>
-      <c r="L108" s="8"/>
+      <c r="L108" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M108" s="8"/>
       <c r="N108" s="8" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3639,10 +3933,13 @@
       <c r="I109" s="8"/>
       <c r="J109" s="8"/>
       <c r="K109" s="8"/>
-      <c r="L109" s="8"/>
+      <c r="L109" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M109" s="8"/>
       <c r="N109" s="8" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3659,49 +3956,57 @@
       <c r="I110" s="9"/>
       <c r="J110" s="9"/>
       <c r="K110" s="9"/>
-      <c r="L110" s="9"/>
+      <c r="L110" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M110" s="9"/>
       <c r="N110" s="9" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="111" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B111" s="53" t="s">
+      <c r="B111" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="C111" s="54"/>
-      <c r="D111" s="54"/>
-      <c r="E111" s="54"/>
-      <c r="F111" s="54"/>
-      <c r="G111" s="54"/>
+      <c r="C111" s="52"/>
+      <c r="D111" s="52"/>
+      <c r="E111" s="52"/>
+      <c r="F111" s="52"/>
+      <c r="G111" s="52"/>
       <c r="H111" s="1" t="e">
         <f>AVERAGE(H11:H110)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I111" s="1" t="e">
-        <f t="shared" ref="I111:O111" si="4">AVERAGE(I11:I110)</f>
+        <f t="shared" ref="I111:N111" si="6">AVERAGE(I11:I110)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J111" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L111" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L111" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="M111" s="1" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N111" s="1" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="G6:H6"/>
     <mergeCell ref="B111:G111"/>
     <mergeCell ref="O9:O10"/>
     <mergeCell ref="P9:P10"/>
@@ -3713,11 +4018,6 @@
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="M9:M10"/>
     <mergeCell ref="N9:N10"/>
-    <mergeCell ref="B1:N1"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="G6:H6"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:D10"/>
@@ -3764,75 +4064,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
       <c r="N1" s="12"/>
     </row>
     <row r="2" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
       <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
       <c r="N3" s="13"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
       <c r="N4" s="13"/>
     </row>
     <row r="5" spans="1:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -3840,8 +4140,8 @@
       <c r="A6" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="52"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="46"/>
       <c r="F6" s="18" t="s">
         <v>0</v>
       </c>
@@ -3854,8 +4154,8 @@
       <c r="A8" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="52"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="46"/>
       <c r="F8" s="18" t="s">
         <v>31</v>
       </c>
@@ -3867,53 +4167,53 @@
       <c r="A9" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="52"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="46"/>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19"/>
       <c r="B10" s="19"/>
     </row>
     <row r="11" spans="1:27" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="50"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="44"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="20"/>
-      <c r="O11" s="48" t="s">
+      <c r="O11" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="P11" s="49"/>
-      <c r="Q11" s="49"/>
-      <c r="R11" s="49"/>
-      <c r="S11" s="49"/>
-      <c r="T11" s="50"/>
-      <c r="V11" s="48" t="s">
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="44"/>
+      <c r="V11" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="W11" s="49"/>
-      <c r="X11" s="49"/>
-      <c r="Y11" s="49"/>
-      <c r="Z11" s="49"/>
-      <c r="AA11" s="50"/>
+      <c r="W11" s="43"/>
+      <c r="X11" s="43"/>
+      <c r="Y11" s="43"/>
+      <c r="Z11" s="43"/>
+      <c r="AA11" s="44"/>
     </row>
     <row r="12" spans="1:27" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="41"/>
-      <c r="B12" s="41"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="48"/>
       <c r="C12" s="6" t="s">
         <v>36</v>
       </c>
@@ -3989,27 +4289,27 @@
         <v>1</v>
       </c>
       <c r="B13" s="22"/>
-      <c r="C13" s="55">
+      <c r="C13" s="40">
         <f>IF(SUM($V13:$AA13), ROUND(V13/SUM($V13:$AA13), 2),0)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="55">
+      <c r="D13" s="40">
         <f t="shared" ref="D13:H28" si="0">IF(SUM($V13:$AA13), ROUND(W13/SUM($V13:$AA13), 2),0)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F13" s="55">
+      <c r="F13" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G13" s="55">
+      <c r="G13" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="55">
+      <c r="H13" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4069,27 +4369,27 @@
         <v>2</v>
       </c>
       <c r="B14" s="25"/>
-      <c r="C14" s="55">
+      <c r="C14" s="40">
         <f t="shared" ref="C14:H68" si="2">IF(SUM($V14:$AA14), ROUND(V14/SUM($V14:$AA14), 2),0)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F14" s="55">
+      <c r="F14" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="55">
+      <c r="H14" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4149,27 +4449,27 @@
         <v>3</v>
       </c>
       <c r="B15" s="25"/>
-      <c r="C15" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D15" s="55">
+      <c r="C15" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D15" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E15" s="55">
+      <c r="E15" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G15" s="55">
+      <c r="G15" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="55">
+      <c r="H15" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4229,27 +4529,27 @@
         <v>4</v>
       </c>
       <c r="B16" s="25"/>
-      <c r="C16" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D16" s="55">
+      <c r="C16" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D16" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E16" s="55">
+      <c r="E16" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="55">
+      <c r="F16" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="55">
+      <c r="G16" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="55">
+      <c r="H16" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4309,27 +4609,27 @@
         <v>5</v>
       </c>
       <c r="B17" s="25"/>
-      <c r="C17" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D17" s="55">
+      <c r="C17" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D17" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E17" s="55">
+      <c r="E17" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F17" s="55">
+      <c r="F17" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="55">
+      <c r="G17" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="55">
+      <c r="H17" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4389,27 +4689,27 @@
         <v>6</v>
       </c>
       <c r="B18" s="25"/>
-      <c r="C18" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D18" s="55">
+      <c r="C18" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D18" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F18" s="55">
+      <c r="F18" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="55">
+      <c r="H18" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4469,27 +4769,27 @@
         <v>7</v>
       </c>
       <c r="B19" s="25"/>
-      <c r="C19" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D19" s="55">
+      <c r="C19" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D19" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E19" s="55">
+      <c r="E19" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F19" s="55">
+      <c r="F19" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G19" s="55">
+      <c r="G19" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H19" s="55">
+      <c r="H19" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4549,27 +4849,27 @@
         <v>8</v>
       </c>
       <c r="B20" s="25"/>
-      <c r="C20" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D20" s="55">
+      <c r="C20" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D20" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F20" s="55">
+      <c r="F20" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" s="55">
+      <c r="H20" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4629,27 +4929,27 @@
         <v>9</v>
       </c>
       <c r="B21" s="25"/>
-      <c r="C21" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D21" s="55">
+      <c r="C21" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D21" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E21" s="55">
+      <c r="E21" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F21" s="55">
+      <c r="F21" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H21" s="55">
+      <c r="H21" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4709,27 +5009,27 @@
         <v>10</v>
       </c>
       <c r="B22" s="25"/>
-      <c r="C22" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D22" s="55">
+      <c r="C22" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D22" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F22" s="55">
+      <c r="F22" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G22" s="55">
+      <c r="G22" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H22" s="55">
+      <c r="H22" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4789,27 +5089,27 @@
         <v>11</v>
       </c>
       <c r="B23" s="25"/>
-      <c r="C23" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D23" s="55">
+      <c r="C23" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D23" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E23" s="55">
+      <c r="E23" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F23" s="55">
+      <c r="F23" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G23" s="55">
+      <c r="G23" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H23" s="55">
+      <c r="H23" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4869,27 +5169,27 @@
         <v>12</v>
       </c>
       <c r="B24" s="25"/>
-      <c r="C24" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D24" s="55">
+      <c r="C24" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D24" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E24" s="55">
+      <c r="E24" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F24" s="55">
+      <c r="F24" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G24" s="55">
+      <c r="G24" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H24" s="55">
+      <c r="H24" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4949,27 +5249,27 @@
         <v>13</v>
       </c>
       <c r="B25" s="25"/>
-      <c r="C25" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D25" s="55">
+      <c r="C25" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D25" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F25" s="55">
+      <c r="F25" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G25" s="55">
+      <c r="G25" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H25" s="55">
+      <c r="H25" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5029,27 +5329,27 @@
         <v>14</v>
       </c>
       <c r="B26" s="25"/>
-      <c r="C26" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D26" s="55">
+      <c r="C26" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="55">
+      <c r="E26" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F26" s="55">
+      <c r="F26" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G26" s="55">
+      <c r="G26" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H26" s="55">
+      <c r="H26" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5109,27 +5409,27 @@
         <v>15</v>
       </c>
       <c r="B27" s="25"/>
-      <c r="C27" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D27" s="55">
+      <c r="C27" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E27" s="55">
+      <c r="E27" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F27" s="55">
+      <c r="F27" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G27" s="55">
+      <c r="G27" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H27" s="55">
+      <c r="H27" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5189,27 +5489,27 @@
         <v>16</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D28" s="55">
+      <c r="C28" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="55">
+      <c r="E28" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F28" s="55">
+      <c r="F28" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G28" s="55">
+      <c r="G28" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H28" s="55">
+      <c r="H28" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5269,27 +5569,27 @@
         <v>17</v>
       </c>
       <c r="B29" s="25"/>
-      <c r="C29" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D29" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E29" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="55">
+      <c r="C29" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5349,27 +5649,27 @@
         <v>18</v>
       </c>
       <c r="B30" s="25"/>
-      <c r="C30" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D30" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E30" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="55">
+      <c r="C30" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5429,27 +5729,27 @@
         <v>19</v>
       </c>
       <c r="B31" s="25"/>
-      <c r="C31" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D31" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E31" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F31" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="55">
+      <c r="C31" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E31" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5509,27 +5809,27 @@
         <v>20</v>
       </c>
       <c r="B32" s="25"/>
-      <c r="C32" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D32" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E32" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F32" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="55">
+      <c r="C32" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E32" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5589,27 +5889,27 @@
         <v>21</v>
       </c>
       <c r="B33" s="25"/>
-      <c r="C33" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D33" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E33" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="55">
+      <c r="C33" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E33" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5669,27 +5969,27 @@
         <v>22</v>
       </c>
       <c r="B34" s="25"/>
-      <c r="C34" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D34" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E34" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F34" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G34" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="55">
+      <c r="C34" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E34" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5749,27 +6049,27 @@
         <v>23</v>
       </c>
       <c r="B35" s="25"/>
-      <c r="C35" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D35" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E35" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="55">
+      <c r="C35" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E35" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5829,27 +6129,27 @@
         <v>24</v>
       </c>
       <c r="B36" s="25"/>
-      <c r="C36" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D36" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E36" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="55">
+      <c r="C36" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E36" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5909,27 +6209,27 @@
         <v>25</v>
       </c>
       <c r="B37" s="25"/>
-      <c r="C37" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D37" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E37" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F37" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G37" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="55">
+      <c r="C37" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E37" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5989,27 +6289,27 @@
         <v>26</v>
       </c>
       <c r="B38" s="25"/>
-      <c r="C38" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D38" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E38" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G38" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="55">
+      <c r="C38" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E38" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6069,27 +6369,27 @@
         <v>27</v>
       </c>
       <c r="B39" s="25"/>
-      <c r="C39" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D39" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E39" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F39" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H39" s="55">
+      <c r="C39" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E39" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6149,27 +6449,27 @@
         <v>28</v>
       </c>
       <c r="B40" s="25"/>
-      <c r="C40" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D40" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E40" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="55">
+      <c r="C40" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E40" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6229,27 +6529,27 @@
         <v>29</v>
       </c>
       <c r="B41" s="25"/>
-      <c r="C41" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D41" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E41" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F41" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G41" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="55">
+      <c r="C41" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E41" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G41" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6309,27 +6609,27 @@
         <v>30</v>
       </c>
       <c r="B42" s="25"/>
-      <c r="C42" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D42" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E42" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F42" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G42" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="55">
+      <c r="C42" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E42" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G42" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6389,27 +6689,27 @@
         <v>31</v>
       </c>
       <c r="B43" s="25"/>
-      <c r="C43" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D43" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E43" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F43" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G43" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H43" s="55">
+      <c r="C43" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E43" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G43" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6469,27 +6769,27 @@
         <v>32</v>
       </c>
       <c r="B44" s="25"/>
-      <c r="C44" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D44" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E44" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F44" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G44" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H44" s="55">
+      <c r="C44" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E44" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G44" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6549,27 +6849,27 @@
         <v>33</v>
       </c>
       <c r="B45" s="25"/>
-      <c r="C45" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D45" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E45" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F45" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G45" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H45" s="55">
+      <c r="C45" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E45" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G45" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6629,27 +6929,27 @@
         <v>34</v>
       </c>
       <c r="B46" s="25"/>
-      <c r="C46" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D46" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E46" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F46" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G46" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H46" s="55">
+      <c r="C46" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D46" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E46" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G46" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6709,27 +7009,27 @@
         <v>35</v>
       </c>
       <c r="B47" s="25"/>
-      <c r="C47" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D47" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E47" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F47" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G47" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H47" s="55">
+      <c r="C47" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D47" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E47" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F47" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G47" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6789,27 +7089,27 @@
         <v>36</v>
       </c>
       <c r="B48" s="25"/>
-      <c r="C48" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D48" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E48" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G48" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H48" s="55">
+      <c r="C48" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D48" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E48" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G48" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H48" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6869,27 +7169,27 @@
         <v>37</v>
       </c>
       <c r="B49" s="25"/>
-      <c r="C49" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D49" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E49" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G49" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H49" s="55">
+      <c r="C49" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D49" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E49" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6949,27 +7249,27 @@
         <v>38</v>
       </c>
       <c r="B50" s="25"/>
-      <c r="C50" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D50" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E50" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F50" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G50" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="55">
+      <c r="C50" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D50" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E50" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F50" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G50" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7029,27 +7329,27 @@
         <v>39</v>
       </c>
       <c r="B51" s="25"/>
-      <c r="C51" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D51" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E51" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F51" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G51" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H51" s="55">
+      <c r="C51" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D51" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E51" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G51" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H51" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7109,27 +7409,27 @@
         <v>40</v>
       </c>
       <c r="B52" s="25"/>
-      <c r="C52" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D52" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E52" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F52" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G52" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H52" s="55">
+      <c r="C52" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D52" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E52" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F52" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G52" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H52" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7189,27 +7489,27 @@
         <v>41</v>
       </c>
       <c r="B53" s="25"/>
-      <c r="C53" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D53" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E53" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F53" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G53" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H53" s="55">
+      <c r="C53" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D53" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E53" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F53" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G53" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H53" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7269,27 +7569,27 @@
         <v>42</v>
       </c>
       <c r="B54" s="25"/>
-      <c r="C54" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D54" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E54" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F54" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G54" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H54" s="55">
+      <c r="C54" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D54" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E54" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H54" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7349,27 +7649,27 @@
         <v>43</v>
       </c>
       <c r="B55" s="25"/>
-      <c r="C55" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D55" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E55" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F55" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G55" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H55" s="55">
+      <c r="C55" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D55" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E55" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G55" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H55" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7429,27 +7729,27 @@
         <v>44</v>
       </c>
       <c r="B56" s="25"/>
-      <c r="C56" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D56" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E56" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F56" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G56" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H56" s="55">
+      <c r="C56" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D56" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E56" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F56" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G56" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H56" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7509,27 +7809,27 @@
         <v>45</v>
       </c>
       <c r="B57" s="25"/>
-      <c r="C57" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D57" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E57" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F57" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G57" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H57" s="55">
+      <c r="C57" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D57" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E57" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F57" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G57" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H57" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7589,27 +7889,27 @@
         <v>46</v>
       </c>
       <c r="B58" s="25"/>
-      <c r="C58" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D58" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E58" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F58" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G58" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H58" s="55">
+      <c r="C58" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D58" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E58" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F58" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G58" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7669,27 +7969,27 @@
         <v>47</v>
       </c>
       <c r="B59" s="25"/>
-      <c r="C59" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D59" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E59" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F59" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G59" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H59" s="55">
+      <c r="C59" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D59" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E59" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F59" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G59" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H59" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7749,27 +8049,27 @@
         <v>48</v>
       </c>
       <c r="B60" s="25"/>
-      <c r="C60" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D60" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E60" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F60" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G60" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H60" s="55">
+      <c r="C60" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D60" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E60" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F60" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G60" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H60" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7829,27 +8129,27 @@
         <v>49</v>
       </c>
       <c r="B61" s="25"/>
-      <c r="C61" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D61" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E61" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F61" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G61" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H61" s="55">
+      <c r="C61" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D61" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E61" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F61" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G61" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H61" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7909,27 +8209,27 @@
         <v>50</v>
       </c>
       <c r="B62" s="25"/>
-      <c r="C62" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D62" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E62" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F62" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G62" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H62" s="55">
+      <c r="C62" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D62" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E62" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G62" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H62" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7989,27 +8289,27 @@
         <v>51</v>
       </c>
       <c r="B63" s="25"/>
-      <c r="C63" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D63" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E63" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F63" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G63" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H63" s="55">
+      <c r="C63" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D63" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E63" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F63" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G63" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H63" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8069,27 +8369,27 @@
         <v>52</v>
       </c>
       <c r="B64" s="25"/>
-      <c r="C64" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D64" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E64" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F64" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G64" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H64" s="55">
+      <c r="C64" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D64" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E64" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F64" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G64" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H64" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8149,27 +8449,27 @@
         <v>53</v>
       </c>
       <c r="B65" s="25"/>
-      <c r="C65" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D65" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E65" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F65" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G65" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H65" s="55">
+      <c r="C65" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D65" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E65" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F65" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G65" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H65" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8229,27 +8529,27 @@
         <v>54</v>
       </c>
       <c r="B66" s="25"/>
-      <c r="C66" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D66" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E66" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F66" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G66" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H66" s="55">
+      <c r="C66" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D66" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E66" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F66" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G66" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H66" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8309,27 +8609,27 @@
         <v>55</v>
       </c>
       <c r="B67" s="25"/>
-      <c r="C67" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D67" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E67" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F67" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G67" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H67" s="55">
+      <c r="C67" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D67" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E67" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F67" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G67" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H67" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8389,27 +8689,27 @@
         <v>56</v>
       </c>
       <c r="B68" s="25"/>
-      <c r="C68" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D68" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E68" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F68" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G68" s="55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H68" s="55">
+      <c r="C68" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D68" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E68" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F68" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G68" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H68" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8469,27 +8769,27 @@
         <v>57</v>
       </c>
       <c r="B69" s="25"/>
-      <c r="C69" s="55">
+      <c r="C69" s="40">
         <f t="shared" ref="C69:H111" si="9">IF(SUM($V69:$AA69), ROUND(V69/SUM($V69:$AA69), 2),0)</f>
         <v>0</v>
       </c>
-      <c r="D69" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E69" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F69" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G69" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H69" s="55">
+      <c r="D69" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E69" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F69" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G69" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H69" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8549,27 +8849,27 @@
         <v>58</v>
       </c>
       <c r="B70" s="25"/>
-      <c r="C70" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D70" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E70" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F70" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G70" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H70" s="55">
+      <c r="C70" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D70" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E70" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F70" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G70" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H70" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8629,27 +8929,27 @@
         <v>59</v>
       </c>
       <c r="B71" s="25"/>
-      <c r="C71" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D71" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E71" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F71" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G71" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H71" s="55">
+      <c r="C71" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D71" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E71" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F71" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G71" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H71" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8709,27 +9009,27 @@
         <v>60</v>
       </c>
       <c r="B72" s="25"/>
-      <c r="C72" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D72" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E72" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F72" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G72" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H72" s="55">
+      <c r="C72" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D72" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E72" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F72" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G72" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H72" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8789,27 +9089,27 @@
         <v>61</v>
       </c>
       <c r="B73" s="25"/>
-      <c r="C73" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D73" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E73" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F73" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G73" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H73" s="55">
+      <c r="C73" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D73" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E73" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F73" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G73" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H73" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8869,27 +9169,27 @@
         <v>62</v>
       </c>
       <c r="B74" s="25"/>
-      <c r="C74" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D74" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E74" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F74" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G74" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H74" s="55">
+      <c r="C74" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D74" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E74" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F74" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G74" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H74" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -8949,27 +9249,27 @@
         <v>63</v>
       </c>
       <c r="B75" s="25"/>
-      <c r="C75" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D75" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E75" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F75" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G75" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H75" s="55">
+      <c r="C75" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D75" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E75" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F75" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G75" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H75" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9029,27 +9329,27 @@
         <v>64</v>
       </c>
       <c r="B76" s="25"/>
-      <c r="C76" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D76" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E76" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F76" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G76" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H76" s="55">
+      <c r="C76" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D76" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E76" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F76" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G76" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H76" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9109,27 +9409,27 @@
         <v>65</v>
       </c>
       <c r="B77" s="25"/>
-      <c r="C77" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D77" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E77" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F77" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G77" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H77" s="55">
+      <c r="C77" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D77" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E77" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F77" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G77" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H77" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9189,27 +9489,27 @@
         <v>66</v>
       </c>
       <c r="B78" s="25"/>
-      <c r="C78" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D78" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E78" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F78" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G78" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H78" s="55">
+      <c r="C78" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D78" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E78" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F78" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G78" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H78" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9269,27 +9569,27 @@
         <v>67</v>
       </c>
       <c r="B79" s="25"/>
-      <c r="C79" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D79" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E79" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F79" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G79" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H79" s="55">
+      <c r="C79" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D79" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E79" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F79" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G79" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H79" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9349,27 +9649,27 @@
         <v>68</v>
       </c>
       <c r="B80" s="25"/>
-      <c r="C80" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D80" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E80" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F80" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G80" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H80" s="55">
+      <c r="C80" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D80" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E80" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F80" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G80" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H80" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9429,27 +9729,27 @@
         <v>69</v>
       </c>
       <c r="B81" s="25"/>
-      <c r="C81" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D81" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E81" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F81" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G81" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H81" s="55">
+      <c r="C81" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D81" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E81" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F81" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G81" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H81" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9509,27 +9809,27 @@
         <v>70</v>
       </c>
       <c r="B82" s="25"/>
-      <c r="C82" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D82" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E82" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F82" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G82" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H82" s="55">
+      <c r="C82" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D82" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E82" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F82" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G82" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H82" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9589,27 +9889,27 @@
         <v>71</v>
       </c>
       <c r="B83" s="25"/>
-      <c r="C83" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D83" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E83" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F83" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G83" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H83" s="55">
+      <c r="C83" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D83" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E83" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F83" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G83" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H83" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9669,27 +9969,27 @@
         <v>72</v>
       </c>
       <c r="B84" s="25"/>
-      <c r="C84" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D84" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E84" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F84" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G84" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H84" s="55">
+      <c r="C84" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D84" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E84" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F84" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G84" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H84" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9749,27 +10049,27 @@
         <v>73</v>
       </c>
       <c r="B85" s="25"/>
-      <c r="C85" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D85" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E85" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F85" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G85" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H85" s="55">
+      <c r="C85" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D85" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E85" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F85" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G85" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H85" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9829,27 +10129,27 @@
         <v>74</v>
       </c>
       <c r="B86" s="25"/>
-      <c r="C86" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D86" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E86" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F86" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G86" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H86" s="55">
+      <c r="C86" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D86" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E86" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F86" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G86" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H86" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9909,27 +10209,27 @@
         <v>75</v>
       </c>
       <c r="B87" s="25"/>
-      <c r="C87" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D87" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E87" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F87" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G87" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H87" s="55">
+      <c r="C87" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D87" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E87" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F87" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G87" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H87" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -9989,27 +10289,27 @@
         <v>76</v>
       </c>
       <c r="B88" s="25"/>
-      <c r="C88" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D88" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E88" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F88" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G88" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H88" s="55">
+      <c r="C88" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D88" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E88" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F88" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G88" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H88" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10069,27 +10369,27 @@
         <v>77</v>
       </c>
       <c r="B89" s="25"/>
-      <c r="C89" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D89" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E89" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F89" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G89" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H89" s="55">
+      <c r="C89" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D89" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E89" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F89" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G89" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H89" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10149,27 +10449,27 @@
         <v>78</v>
       </c>
       <c r="B90" s="25"/>
-      <c r="C90" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D90" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E90" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F90" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G90" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H90" s="55">
+      <c r="C90" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D90" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E90" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F90" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G90" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H90" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10229,27 +10529,27 @@
         <v>79</v>
       </c>
       <c r="B91" s="25"/>
-      <c r="C91" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D91" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E91" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F91" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G91" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H91" s="55">
+      <c r="C91" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D91" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E91" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F91" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G91" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H91" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10309,27 +10609,27 @@
         <v>80</v>
       </c>
       <c r="B92" s="25"/>
-      <c r="C92" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D92" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E92" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F92" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G92" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H92" s="55">
+      <c r="C92" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D92" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E92" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F92" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G92" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H92" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10389,27 +10689,27 @@
         <v>81</v>
       </c>
       <c r="B93" s="25"/>
-      <c r="C93" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D93" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E93" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F93" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G93" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H93" s="55">
+      <c r="C93" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D93" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E93" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F93" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G93" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H93" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10469,27 +10769,27 @@
         <v>82</v>
       </c>
       <c r="B94" s="25"/>
-      <c r="C94" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D94" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E94" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F94" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G94" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H94" s="55">
+      <c r="C94" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D94" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E94" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F94" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G94" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H94" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10549,27 +10849,27 @@
         <v>83</v>
       </c>
       <c r="B95" s="25"/>
-      <c r="C95" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D95" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E95" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F95" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G95" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H95" s="55">
+      <c r="C95" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D95" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E95" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F95" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G95" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H95" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10629,27 +10929,27 @@
         <v>84</v>
       </c>
       <c r="B96" s="25"/>
-      <c r="C96" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D96" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E96" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F96" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G96" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H96" s="55">
+      <c r="C96" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D96" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E96" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F96" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G96" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H96" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10709,27 +11009,27 @@
         <v>85</v>
       </c>
       <c r="B97" s="25"/>
-      <c r="C97" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D97" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E97" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F97" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G97" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H97" s="55">
+      <c r="C97" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D97" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E97" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F97" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G97" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H97" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10789,27 +11089,27 @@
         <v>86</v>
       </c>
       <c r="B98" s="25"/>
-      <c r="C98" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D98" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E98" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F98" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G98" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H98" s="55">
+      <c r="C98" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D98" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E98" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F98" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G98" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H98" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10869,27 +11169,27 @@
         <v>87</v>
       </c>
       <c r="B99" s="25"/>
-      <c r="C99" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D99" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E99" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F99" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G99" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H99" s="55">
+      <c r="C99" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D99" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E99" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F99" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G99" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H99" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10949,27 +11249,27 @@
         <v>88</v>
       </c>
       <c r="B100" s="25"/>
-      <c r="C100" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D100" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E100" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F100" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G100" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H100" s="55">
+      <c r="C100" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D100" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E100" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F100" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G100" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H100" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11029,27 +11329,27 @@
         <v>89</v>
       </c>
       <c r="B101" s="25"/>
-      <c r="C101" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D101" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E101" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F101" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G101" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H101" s="55">
+      <c r="C101" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D101" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E101" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F101" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G101" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H101" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11109,27 +11409,27 @@
         <v>90</v>
       </c>
       <c r="B102" s="25"/>
-      <c r="C102" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D102" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E102" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F102" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G102" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H102" s="55">
+      <c r="C102" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D102" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E102" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F102" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G102" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H102" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11189,27 +11489,27 @@
         <v>91</v>
       </c>
       <c r="B103" s="25"/>
-      <c r="C103" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D103" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E103" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F103" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G103" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H103" s="55">
+      <c r="C103" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D103" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E103" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F103" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G103" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H103" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11269,27 +11569,27 @@
         <v>92</v>
       </c>
       <c r="B104" s="25"/>
-      <c r="C104" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D104" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E104" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F104" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G104" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H104" s="55">
+      <c r="C104" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D104" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E104" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F104" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G104" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H104" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11349,27 +11649,27 @@
         <v>93</v>
       </c>
       <c r="B105" s="25"/>
-      <c r="C105" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D105" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E105" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F105" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G105" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H105" s="55">
+      <c r="C105" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D105" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E105" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F105" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G105" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H105" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11429,27 +11729,27 @@
         <v>94</v>
       </c>
       <c r="B106" s="25"/>
-      <c r="C106" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D106" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E106" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F106" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G106" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H106" s="55">
+      <c r="C106" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D106" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E106" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F106" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G106" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H106" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11509,27 +11809,27 @@
         <v>95</v>
       </c>
       <c r="B107" s="25"/>
-      <c r="C107" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D107" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E107" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F107" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G107" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H107" s="55">
+      <c r="C107" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D107" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E107" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F107" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G107" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H107" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11589,27 +11889,27 @@
         <v>96</v>
       </c>
       <c r="B108" s="25"/>
-      <c r="C108" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D108" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E108" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F108" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G108" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H108" s="55">
+      <c r="C108" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D108" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E108" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F108" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G108" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H108" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11669,27 +11969,27 @@
         <v>97</v>
       </c>
       <c r="B109" s="25"/>
-      <c r="C109" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D109" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E109" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F109" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G109" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H109" s="55">
+      <c r="C109" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D109" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E109" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F109" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G109" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H109" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11749,27 +12049,27 @@
         <v>98</v>
       </c>
       <c r="B110" s="25"/>
-      <c r="C110" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D110" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E110" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F110" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G110" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H110" s="55">
+      <c r="C110" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D110" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E110" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F110" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G110" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H110" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -11829,27 +12129,27 @@
         <v>99</v>
       </c>
       <c r="B111" s="25"/>
-      <c r="C111" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D111" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E111" s="55">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F111" s="55">
+      <c r="C111" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="D111" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E111" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F111" s="40">
         <f t="shared" ref="F111:H112" si="17">IF(SUM($V111:$AA111), ROUND(Y111/SUM($V111:$AA111), 2),0)</f>
         <v>0</v>
       </c>
-      <c r="G111" s="55">
+      <c r="G111" s="40">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H111" s="55">
+      <c r="H111" s="40">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
@@ -11909,27 +12209,27 @@
         <v>100</v>
       </c>
       <c r="B112" s="27"/>
-      <c r="C112" s="56">
+      <c r="C112" s="41">
         <f t="shared" ref="C112:E112" si="18">IF(SUM($V112:$AA112), ROUND(V112/SUM($V112:$AA112), 2),0)</f>
         <v>0</v>
       </c>
-      <c r="D112" s="56">
+      <c r="D112" s="41">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="E112" s="56">
+      <c r="E112" s="41">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="F112" s="56">
+      <c r="F112" s="41">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G112" s="56">
+      <c r="G112" s="41">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H112" s="56">
+      <c r="H112" s="41">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
@@ -11990,7 +12290,7 @@
         <v>47</v>
       </c>
       <c r="B113" s="21">
-        <f t="shared" ref="B113:H113" si="19">COUNT(B13:B112)</f>
+        <f t="shared" ref="B113" si="19">COUNT(B13:B112)</f>
         <v>0</v>
       </c>
       <c r="C113" s="21">
@@ -12323,18 +12623,18 @@
     <row r="124" spans="1:21" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="V11:AA11"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="O11:T11"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="18" orientation="portrait" r:id="rId1"/>

--- a/templates/1.2. Dozer _ Template_2026_05_01_BiT.xlsx
+++ b/templates/1.2. Dozer _ Template_2026_05_01_BiT.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\CMI_DATA_PROCESSOR\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\CMI-NPN\CMI-DATABASE\Templates-BiT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49B797A-9A66-4623-B2E1-7EC28E831D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807ECDAF-F8BB-4DED-B758-645FC626BF0C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="1380" windowWidth="20490" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dozer" sheetId="22" r:id="rId1"/>
-    <sheet name="MPDM 1" sheetId="11" r:id="rId2"/>
+    <sheet name="MPDM" sheetId="11" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Dozer!$A$1:$R$111</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'MPDM 1'!$A$1:$T$120</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">MPDM!$A$1:$T$120</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -570,10 +577,12 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -966,6 +975,18 @@
     <xf numFmtId="43" fontId="3" fillId="7" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -975,16 +996,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -993,15 +1005,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1009,6 +1012,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1442,72 +1451,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="108.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
     </row>
     <row r="2" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
     </row>
     <row r="3" spans="2:18" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
     </row>
     <row r="5" spans="2:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:18" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1516,10 +1525,10 @@
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="11"/>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="56"/>
+      <c r="H6" s="54"/>
       <c r="I6" s="2"/>
       <c r="K6" s="3" t="s">
         <v>0</v>
@@ -1541,61 +1550,61 @@
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="2:18" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="47" t="s">
+      <c r="E9" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="47" t="s">
+      <c r="G9" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="42" t="s">
+      <c r="H9" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="43"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="47" t="s">
+      <c r="I9" s="47"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="L9" s="47" t="s">
+      <c r="L9" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="M9" s="47" t="s">
+      <c r="M9" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="N9" s="47" t="s">
+      <c r="N9" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="O9" s="47" t="s">
+      <c r="O9" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="P9" s="47" t="s">
+      <c r="P9" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="Q9" s="47" t="s">
+      <c r="Q9" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="R9" s="47" t="s">
+      <c r="R9" s="44" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="2:18" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
       <c r="H10" s="6" t="s">
         <v>17</v>
       </c>
@@ -1605,14 +1614,14 @@
       <c r="J10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="48"/>
-      <c r="P10" s="48"/>
-      <c r="Q10" s="48"/>
-      <c r="R10" s="48"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="45"/>
+      <c r="M10" s="45"/>
+      <c r="N10" s="45"/>
+      <c r="O10" s="45"/>
+      <c r="P10" s="45"/>
+      <c r="Q10" s="45"/>
+      <c r="R10" s="45"/>
     </row>
     <row r="11" spans="2:18" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="7" t="s">
@@ -1627,29 +1636,26 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="7">
-        <f>H11*I11*J11</f>
-        <v>0</v>
-      </c>
+      <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7" t="e">
         <f>L11*3600/M11*0.764555</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O11" s="38" t="e">
-        <f>'MPDM 1'!H118</f>
+        <f>MPDM!H118</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P11" s="38" t="e">
-        <f>'MPDM 1'!K118*L11</f>
+        <f>MPDM!K118*L11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q11" s="39" t="e">
-        <f>'MPDM 1'!H119*L11</f>
+        <f>MPDM!H119*L11</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R11" s="39" t="e">
-        <f>'MPDM 1'!K119</f>
+        <f>MPDM!K119</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1666,10 +1672,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
-      <c r="L12" s="8">
-        <f>H12*I12*J12</f>
-        <v>0</v>
-      </c>
+      <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8" t="e">
         <f t="shared" ref="N12:N21" si="0">L12*3600/M12*0.764555</f>
@@ -1693,10 +1696,7 @@
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
-      <c r="L13" s="8">
-        <f t="shared" ref="L13:L76" si="1">H13*I13*J13</f>
-        <v>0</v>
-      </c>
+      <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8" t="e">
         <f t="shared" si="0"/>
@@ -1720,10 +1720,7 @@
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
-      <c r="L14" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8" t="e">
         <f t="shared" si="0"/>
@@ -1747,10 +1744,7 @@
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
-      <c r="L15" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L15" s="9"/>
       <c r="M15" s="9"/>
       <c r="N15" s="9" t="e">
         <f t="shared" si="0"/>
@@ -1774,10 +1768,7 @@
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
-      <c r="L16" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L16" s="7"/>
       <c r="M16" s="7"/>
       <c r="N16" s="7" t="e">
         <f t="shared" si="0"/>
@@ -1801,10 +1792,7 @@
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
-      <c r="L17" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8" t="e">
         <f t="shared" si="0"/>
@@ -1828,10 +1816,7 @@
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
-      <c r="L18" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L18" s="8"/>
       <c r="M18" s="8"/>
       <c r="N18" s="8" t="e">
         <f t="shared" si="0"/>
@@ -1855,10 +1840,7 @@
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
-      <c r="L19" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8" t="e">
         <f t="shared" si="0"/>
@@ -1882,10 +1864,7 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L20" s="9"/>
       <c r="M20" s="9"/>
       <c r="N20" s="9" t="e">
         <f t="shared" si="0"/>
@@ -1909,10 +1888,7 @@
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
-      <c r="L21" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L21" s="7"/>
       <c r="M21" s="7"/>
       <c r="N21" s="7" t="e">
         <f t="shared" si="0"/>
@@ -1932,13 +1908,10 @@
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
-      <c r="L22" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8" t="e">
-        <f t="shared" ref="N22:N85" si="2">L22*3600/M22*0.764555</f>
+        <f t="shared" ref="N22:N85" si="1">L22*3600/M22*0.764555</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1955,13 +1928,10 @@
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
-      <c r="L23" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1978,13 +1948,10 @@
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
-      <c r="L24" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2001,13 +1968,10 @@
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L25" s="9"/>
       <c r="M25" s="9"/>
       <c r="N25" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2024,13 +1988,10 @@
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
-      <c r="L26" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L26" s="7"/>
       <c r="M26" s="7"/>
       <c r="N26" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2047,13 +2008,10 @@
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
-      <c r="L27" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L27" s="8"/>
       <c r="M27" s="8"/>
       <c r="N27" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2070,13 +2028,10 @@
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
-      <c r="L28" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L28" s="8"/>
       <c r="M28" s="8"/>
       <c r="N28" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2093,13 +2048,10 @@
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
-      <c r="L29" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L29" s="8"/>
       <c r="M29" s="8"/>
       <c r="N29" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2116,13 +2068,10 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L30" s="9"/>
       <c r="M30" s="9"/>
       <c r="N30" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2139,13 +2088,10 @@
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
-      <c r="L31" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L31" s="7"/>
       <c r="M31" s="7"/>
       <c r="N31" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2162,13 +2108,10 @@
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
-      <c r="L32" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L32" s="8"/>
       <c r="M32" s="8"/>
       <c r="N32" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2185,13 +2128,10 @@
       <c r="I33" s="8"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
-      <c r="L33" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L33" s="8"/>
       <c r="M33" s="8"/>
       <c r="N33" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2208,13 +2148,10 @@
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
-      <c r="L34" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L34" s="8"/>
       <c r="M34" s="8"/>
       <c r="N34" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2231,13 +2168,10 @@
       <c r="I35" s="9"/>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
-      <c r="L35" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L35" s="9"/>
       <c r="M35" s="9"/>
       <c r="N35" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2254,13 +2188,10 @@
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
-      <c r="L36" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L36" s="7"/>
       <c r="M36" s="7"/>
       <c r="N36" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2277,13 +2208,10 @@
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
-      <c r="L37" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L37" s="8"/>
       <c r="M37" s="8"/>
       <c r="N37" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2300,13 +2228,10 @@
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
-      <c r="L38" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L38" s="8"/>
       <c r="M38" s="8"/>
       <c r="N38" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2323,13 +2248,10 @@
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
-      <c r="L39" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L39" s="8"/>
       <c r="M39" s="8"/>
       <c r="N39" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2346,13 +2268,10 @@
       <c r="I40" s="9"/>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
-      <c r="L40" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L40" s="9"/>
       <c r="M40" s="9"/>
       <c r="N40" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2369,13 +2288,10 @@
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
-      <c r="L41" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L41" s="7"/>
       <c r="M41" s="7"/>
       <c r="N41" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2392,13 +2308,10 @@
       <c r="I42" s="8"/>
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
-      <c r="L42" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2415,13 +2328,10 @@
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
-      <c r="L43" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L43" s="8"/>
       <c r="M43" s="8"/>
       <c r="N43" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2438,13 +2348,10 @@
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
       <c r="K44" s="8"/>
-      <c r="L44" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L44" s="8"/>
       <c r="M44" s="8"/>
       <c r="N44" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2461,13 +2368,10 @@
       <c r="I45" s="9"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
-      <c r="L45" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L45" s="9"/>
       <c r="M45" s="9"/>
       <c r="N45" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2484,13 +2388,10 @@
       <c r="I46" s="7"/>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
-      <c r="L46" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L46" s="7"/>
       <c r="M46" s="7"/>
       <c r="N46" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2507,13 +2408,10 @@
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
-      <c r="L47" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L47" s="8"/>
       <c r="M47" s="8"/>
       <c r="N47" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2530,13 +2428,10 @@
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8"/>
-      <c r="L48" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L48" s="8"/>
       <c r="M48" s="8"/>
       <c r="N48" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2553,13 +2448,10 @@
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
       <c r="K49" s="8"/>
-      <c r="L49" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L49" s="8"/>
       <c r="M49" s="8"/>
       <c r="N49" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2576,13 +2468,10 @@
       <c r="I50" s="9"/>
       <c r="J50" s="9"/>
       <c r="K50" s="9"/>
-      <c r="L50" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L50" s="9"/>
       <c r="M50" s="9"/>
       <c r="N50" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2599,13 +2488,10 @@
       <c r="I51" s="7"/>
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
-      <c r="L51" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L51" s="7"/>
       <c r="M51" s="7"/>
       <c r="N51" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2622,13 +2508,10 @@
       <c r="I52" s="8"/>
       <c r="J52" s="8"/>
       <c r="K52" s="8"/>
-      <c r="L52" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L52" s="8"/>
       <c r="M52" s="8"/>
       <c r="N52" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2645,13 +2528,10 @@
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
       <c r="K53" s="8"/>
-      <c r="L53" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L53" s="8"/>
       <c r="M53" s="8"/>
       <c r="N53" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2668,13 +2548,10 @@
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
       <c r="K54" s="8"/>
-      <c r="L54" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L54" s="8"/>
       <c r="M54" s="8"/>
       <c r="N54" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2691,13 +2568,10 @@
       <c r="I55" s="9"/>
       <c r="J55" s="9"/>
       <c r="K55" s="9"/>
-      <c r="L55" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L55" s="9"/>
       <c r="M55" s="9"/>
       <c r="N55" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2714,13 +2588,10 @@
       <c r="I56" s="7"/>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
-      <c r="L56" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L56" s="7"/>
       <c r="M56" s="7"/>
       <c r="N56" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2737,13 +2608,10 @@
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
       <c r="K57" s="8"/>
-      <c r="L57" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L57" s="8"/>
       <c r="M57" s="8"/>
       <c r="N57" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2760,13 +2628,10 @@
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
       <c r="K58" s="8"/>
-      <c r="L58" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L58" s="8"/>
       <c r="M58" s="8"/>
       <c r="N58" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2783,13 +2648,10 @@
       <c r="I59" s="8"/>
       <c r="J59" s="8"/>
       <c r="K59" s="8"/>
-      <c r="L59" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L59" s="8"/>
       <c r="M59" s="8"/>
       <c r="N59" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2806,13 +2668,10 @@
       <c r="I60" s="9"/>
       <c r="J60" s="9"/>
       <c r="K60" s="9"/>
-      <c r="L60" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L60" s="9"/>
       <c r="M60" s="9"/>
       <c r="N60" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2829,13 +2688,10 @@
       <c r="I61" s="7"/>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
-      <c r="L61" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L61" s="7"/>
       <c r="M61" s="7"/>
       <c r="N61" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2852,13 +2708,10 @@
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
       <c r="K62" s="8"/>
-      <c r="L62" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L62" s="8"/>
       <c r="M62" s="8"/>
       <c r="N62" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2875,13 +2728,10 @@
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
       <c r="K63" s="8"/>
-      <c r="L63" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L63" s="8"/>
       <c r="M63" s="8"/>
       <c r="N63" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2898,13 +2748,10 @@
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
       <c r="K64" s="8"/>
-      <c r="L64" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L64" s="8"/>
       <c r="M64" s="8"/>
       <c r="N64" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2921,13 +2768,10 @@
       <c r="I65" s="9"/>
       <c r="J65" s="9"/>
       <c r="K65" s="9"/>
-      <c r="L65" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L65" s="9"/>
       <c r="M65" s="9"/>
       <c r="N65" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2944,13 +2788,10 @@
       <c r="I66" s="7"/>
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
-      <c r="L66" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L66" s="7"/>
       <c r="M66" s="7"/>
       <c r="N66" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2967,13 +2808,10 @@
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
       <c r="K67" s="8"/>
-      <c r="L67" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L67" s="8"/>
       <c r="M67" s="8"/>
       <c r="N67" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2990,13 +2828,10 @@
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
       <c r="K68" s="8"/>
-      <c r="L68" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L68" s="8"/>
       <c r="M68" s="8"/>
       <c r="N68" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3013,13 +2848,10 @@
       <c r="I69" s="8"/>
       <c r="J69" s="8"/>
       <c r="K69" s="8"/>
-      <c r="L69" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L69" s="8"/>
       <c r="M69" s="8"/>
       <c r="N69" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3036,13 +2868,10 @@
       <c r="I70" s="9"/>
       <c r="J70" s="9"/>
       <c r="K70" s="9"/>
-      <c r="L70" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L70" s="9"/>
       <c r="M70" s="9"/>
       <c r="N70" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3059,13 +2888,10 @@
       <c r="I71" s="7"/>
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
-      <c r="L71" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L71" s="7"/>
       <c r="M71" s="7"/>
       <c r="N71" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3082,13 +2908,10 @@
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
       <c r="K72" s="8"/>
-      <c r="L72" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L72" s="8"/>
       <c r="M72" s="8"/>
       <c r="N72" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3105,13 +2928,10 @@
       <c r="I73" s="8"/>
       <c r="J73" s="8"/>
       <c r="K73" s="8"/>
-      <c r="L73" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L73" s="8"/>
       <c r="M73" s="8"/>
       <c r="N73" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3128,13 +2948,10 @@
       <c r="I74" s="8"/>
       <c r="J74" s="8"/>
       <c r="K74" s="8"/>
-      <c r="L74" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L74" s="8"/>
       <c r="M74" s="8"/>
       <c r="N74" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3151,13 +2968,10 @@
       <c r="I75" s="9"/>
       <c r="J75" s="9"/>
       <c r="K75" s="9"/>
-      <c r="L75" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L75" s="9"/>
       <c r="M75" s="9"/>
       <c r="N75" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3174,13 +2988,10 @@
       <c r="I76" s="7"/>
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
-      <c r="L76" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L76" s="7"/>
       <c r="M76" s="7"/>
       <c r="N76" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3197,13 +3008,10 @@
       <c r="I77" s="8"/>
       <c r="J77" s="8"/>
       <c r="K77" s="8"/>
-      <c r="L77" s="8">
-        <f t="shared" ref="L77:L110" si="3">H77*I77*J77</f>
-        <v>0</v>
-      </c>
+      <c r="L77" s="8"/>
       <c r="M77" s="8"/>
       <c r="N77" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3220,13 +3028,10 @@
       <c r="I78" s="8"/>
       <c r="J78" s="8"/>
       <c r="K78" s="8"/>
-      <c r="L78" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L78" s="8"/>
       <c r="M78" s="8"/>
       <c r="N78" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3243,13 +3048,10 @@
       <c r="I79" s="8"/>
       <c r="J79" s="8"/>
       <c r="K79" s="8"/>
-      <c r="L79" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L79" s="8"/>
       <c r="M79" s="8"/>
       <c r="N79" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3266,13 +3068,10 @@
       <c r="I80" s="9"/>
       <c r="J80" s="9"/>
       <c r="K80" s="9"/>
-      <c r="L80" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L80" s="9"/>
       <c r="M80" s="9"/>
       <c r="N80" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3289,13 +3088,10 @@
       <c r="I81" s="7"/>
       <c r="J81" s="7"/>
       <c r="K81" s="7"/>
-      <c r="L81" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L81" s="7"/>
       <c r="M81" s="7"/>
       <c r="N81" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3312,13 +3108,10 @@
       <c r="I82" s="8"/>
       <c r="J82" s="8"/>
       <c r="K82" s="8"/>
-      <c r="L82" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L82" s="8"/>
       <c r="M82" s="8"/>
       <c r="N82" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3335,13 +3128,10 @@
       <c r="I83" s="8"/>
       <c r="J83" s="8"/>
       <c r="K83" s="8"/>
-      <c r="L83" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L83" s="8"/>
       <c r="M83" s="8"/>
       <c r="N83" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3358,13 +3148,10 @@
       <c r="I84" s="8"/>
       <c r="J84" s="8"/>
       <c r="K84" s="8"/>
-      <c r="L84" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L84" s="8"/>
       <c r="M84" s="8"/>
       <c r="N84" s="8" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3381,13 +3168,10 @@
       <c r="I85" s="9"/>
       <c r="J85" s="9"/>
       <c r="K85" s="9"/>
-      <c r="L85" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L85" s="9"/>
       <c r="M85" s="9"/>
       <c r="N85" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3404,13 +3188,10 @@
       <c r="I86" s="7"/>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
-      <c r="L86" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L86" s="7"/>
       <c r="M86" s="7"/>
       <c r="N86" s="7" t="e">
-        <f t="shared" ref="N86:N105" si="4">L86*3600/M86*0.764555</f>
+        <f t="shared" ref="N86:N105" si="2">L86*3600/M86*0.764555</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3427,13 +3208,10 @@
       <c r="I87" s="8"/>
       <c r="J87" s="8"/>
       <c r="K87" s="8"/>
-      <c r="L87" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L87" s="8"/>
       <c r="M87" s="8"/>
       <c r="N87" s="8" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3450,13 +3228,10 @@
       <c r="I88" s="8"/>
       <c r="J88" s="8"/>
       <c r="K88" s="8"/>
-      <c r="L88" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L88" s="8"/>
       <c r="M88" s="8"/>
       <c r="N88" s="8" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3473,13 +3248,10 @@
       <c r="I89" s="8"/>
       <c r="J89" s="8"/>
       <c r="K89" s="8"/>
-      <c r="L89" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L89" s="8"/>
       <c r="M89" s="8"/>
       <c r="N89" s="8" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3496,13 +3268,10 @@
       <c r="I90" s="9"/>
       <c r="J90" s="9"/>
       <c r="K90" s="9"/>
-      <c r="L90" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L90" s="9"/>
       <c r="M90" s="9"/>
       <c r="N90" s="9" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3519,13 +3288,10 @@
       <c r="I91" s="7"/>
       <c r="J91" s="7"/>
       <c r="K91" s="7"/>
-      <c r="L91" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L91" s="7"/>
       <c r="M91" s="7"/>
       <c r="N91" s="7" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3542,13 +3308,10 @@
       <c r="I92" s="8"/>
       <c r="J92" s="8"/>
       <c r="K92" s="8"/>
-      <c r="L92" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L92" s="8"/>
       <c r="M92" s="8"/>
       <c r="N92" s="8" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3565,13 +3328,10 @@
       <c r="I93" s="8"/>
       <c r="J93" s="8"/>
       <c r="K93" s="8"/>
-      <c r="L93" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L93" s="8"/>
       <c r="M93" s="8"/>
       <c r="N93" s="8" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3588,13 +3348,10 @@
       <c r="I94" s="8"/>
       <c r="J94" s="8"/>
       <c r="K94" s="8"/>
-      <c r="L94" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L94" s="8"/>
       <c r="M94" s="8"/>
       <c r="N94" s="8" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3611,13 +3368,10 @@
       <c r="I95" s="9"/>
       <c r="J95" s="9"/>
       <c r="K95" s="9"/>
-      <c r="L95" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L95" s="9"/>
       <c r="M95" s="9"/>
       <c r="N95" s="9" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3634,13 +3388,10 @@
       <c r="I96" s="7"/>
       <c r="J96" s="7"/>
       <c r="K96" s="7"/>
-      <c r="L96" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L96" s="7"/>
       <c r="M96" s="7"/>
       <c r="N96" s="7" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3657,13 +3408,10 @@
       <c r="I97" s="8"/>
       <c r="J97" s="8"/>
       <c r="K97" s="8"/>
-      <c r="L97" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L97" s="8"/>
       <c r="M97" s="8"/>
       <c r="N97" s="8" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3680,13 +3428,10 @@
       <c r="I98" s="8"/>
       <c r="J98" s="8"/>
       <c r="K98" s="8"/>
-      <c r="L98" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L98" s="8"/>
       <c r="M98" s="8"/>
       <c r="N98" s="8" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3703,13 +3448,10 @@
       <c r="I99" s="8"/>
       <c r="J99" s="8"/>
       <c r="K99" s="8"/>
-      <c r="L99" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L99" s="8"/>
       <c r="M99" s="8"/>
       <c r="N99" s="8" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3726,13 +3468,10 @@
       <c r="I100" s="9"/>
       <c r="J100" s="9"/>
       <c r="K100" s="9"/>
-      <c r="L100" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L100" s="9"/>
       <c r="M100" s="9"/>
       <c r="N100" s="9" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3749,13 +3488,10 @@
       <c r="I101" s="7"/>
       <c r="J101" s="7"/>
       <c r="K101" s="7"/>
-      <c r="L101" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L101" s="7"/>
       <c r="M101" s="7"/>
       <c r="N101" s="7" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3772,13 +3508,10 @@
       <c r="I102" s="8"/>
       <c r="J102" s="8"/>
       <c r="K102" s="8"/>
-      <c r="L102" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L102" s="8"/>
       <c r="M102" s="8"/>
       <c r="N102" s="8" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3795,13 +3528,10 @@
       <c r="I103" s="8"/>
       <c r="J103" s="8"/>
       <c r="K103" s="8"/>
-      <c r="L103" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L103" s="8"/>
       <c r="M103" s="8"/>
       <c r="N103" s="8" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3818,13 +3548,10 @@
       <c r="I104" s="8"/>
       <c r="J104" s="8"/>
       <c r="K104" s="8"/>
-      <c r="L104" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L104" s="8"/>
       <c r="M104" s="8"/>
       <c r="N104" s="8" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3841,13 +3568,10 @@
       <c r="I105" s="9"/>
       <c r="J105" s="9"/>
       <c r="K105" s="9"/>
-      <c r="L105" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L105" s="9"/>
       <c r="M105" s="9"/>
       <c r="N105" s="9" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3864,13 +3588,10 @@
       <c r="I106" s="7"/>
       <c r="J106" s="7"/>
       <c r="K106" s="7"/>
-      <c r="L106" s="7">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L106" s="7"/>
       <c r="M106" s="7"/>
       <c r="N106" s="7" t="e">
-        <f t="shared" ref="N106:N110" si="5">L106*3600/M106*0.764555</f>
+        <f t="shared" ref="N106:N110" si="3">L106*3600/M106*0.764555</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3887,13 +3608,10 @@
       <c r="I107" s="8"/>
       <c r="J107" s="8"/>
       <c r="K107" s="8"/>
-      <c r="L107" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L107" s="8"/>
       <c r="M107" s="8"/>
       <c r="N107" s="8" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3910,13 +3628,10 @@
       <c r="I108" s="8"/>
       <c r="J108" s="8"/>
       <c r="K108" s="8"/>
-      <c r="L108" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L108" s="8"/>
       <c r="M108" s="8"/>
       <c r="N108" s="8" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3933,13 +3648,10 @@
       <c r="I109" s="8"/>
       <c r="J109" s="8"/>
       <c r="K109" s="8"/>
-      <c r="L109" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L109" s="8"/>
       <c r="M109" s="8"/>
       <c r="N109" s="8" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3956,47 +3668,44 @@
       <c r="I110" s="9"/>
       <c r="J110" s="9"/>
       <c r="K110" s="9"/>
-      <c r="L110" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="L110" s="9"/>
       <c r="M110" s="9"/>
       <c r="N110" s="9" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="111" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B111" s="51" t="s">
+      <c r="B111" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="C111" s="52"/>
-      <c r="D111" s="52"/>
-      <c r="E111" s="52"/>
-      <c r="F111" s="52"/>
-      <c r="G111" s="52"/>
+      <c r="C111" s="43"/>
+      <c r="D111" s="43"/>
+      <c r="E111" s="43"/>
+      <c r="F111" s="43"/>
+      <c r="G111" s="43"/>
       <c r="H111" s="1" t="e">
         <f>AVERAGE(H11:H110)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I111" s="1" t="e">
-        <f t="shared" ref="I111:N111" si="6">AVERAGE(I11:I110)</f>
+        <f t="shared" ref="I111:N111" si="4">AVERAGE(I11:I110)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J111" s="1" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L111" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L111" s="1" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="M111" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N111" s="1" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4064,75 +3773,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
       <c r="N1" s="12"/>
     </row>
     <row r="2" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
       <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
       <c r="N3" s="13"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
       <c r="N4" s="13"/>
     </row>
     <row r="5" spans="1:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -4140,8 +3849,8 @@
       <c r="A6" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="46"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="56"/>
       <c r="F6" s="18" t="s">
         <v>0</v>
       </c>
@@ -4154,8 +3863,8 @@
       <c r="A8" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="46"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="56"/>
       <c r="F8" s="18" t="s">
         <v>31</v>
       </c>
@@ -4167,53 +3876,53 @@
       <c r="A9" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="46"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="56"/>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19"/>
       <c r="B10" s="19"/>
     </row>
     <row r="11" spans="1:27" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="44"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="48"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="20"/>
-      <c r="O11" s="42" t="s">
+      <c r="O11" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="44"/>
-      <c r="V11" s="42" t="s">
+      <c r="P11" s="47"/>
+      <c r="Q11" s="47"/>
+      <c r="R11" s="47"/>
+      <c r="S11" s="47"/>
+      <c r="T11" s="48"/>
+      <c r="V11" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="W11" s="43"/>
-      <c r="X11" s="43"/>
-      <c r="Y11" s="43"/>
-      <c r="Z11" s="43"/>
-      <c r="AA11" s="44"/>
+      <c r="W11" s="47"/>
+      <c r="X11" s="47"/>
+      <c r="Y11" s="47"/>
+      <c r="Z11" s="47"/>
+      <c r="AA11" s="48"/>
     </row>
     <row r="12" spans="1:27" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="48"/>
-      <c r="B12" s="48"/>
+      <c r="A12" s="45"/>
+      <c r="B12" s="45"/>
       <c r="C12" s="6" t="s">
         <v>36</v>
       </c>
